--- a/TRANSACTIONS_all.xlsx
+++ b/TRANSACTIONS_all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aecf56309e6168f4/Documents/comunio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="271" documentId="8_{B00F7E9F-5C85-449B-834E-0179FBCEE2D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F71B40A0-EEE1-4E06-87C1-2E5B0F8B9D72}"/>
+  <xr:revisionPtr revIDLastSave="272" documentId="8_{B00F7E9F-5C85-449B-834E-0179FBCEE2D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D27F7400-FB83-4018-BCBD-965B8AD9F24C}"/>
   <bookViews>
     <workbookView xWindow="6660" yWindow="2700" windowWidth="28800" windowHeight="15370" xr2:uid="{607DE709-F91E-4262-9941-1066BBEC319E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Spieler</t>
   </si>
@@ -50,19 +50,7 @@
     <t>Transaktion</t>
   </si>
   <si>
-    <t>Alfons</t>
-  </si>
-  <si>
     <t>Begründung</t>
-  </si>
-  <si>
-    <t>Transfer annuliert</t>
-  </si>
-  <si>
-    <t>Disziplinarstrafe: Hranac</t>
-  </si>
-  <si>
-    <t>01.06.2025</t>
   </si>
 </sst>
 </file>
@@ -488,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93EB6F54-7766-4759-97DF-03549A275A7C}">
-  <dimension ref="A1:L1135"/>
+  <dimension ref="A1:L1133"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.90625" style="6"/>
@@ -510,7 +498,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -522,18 +510,10 @@
       <c r="L1" s="1"/>
     </row>
     <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>1660000</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="A2" s="7"/>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
       <c r="E2" s="5"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
@@ -544,18 +524,10 @@
       <c r="L2" s="6"/>
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>-166000</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
+      <c r="A3" s="7"/>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
       <c r="E3" s="5"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
@@ -1181,11 +1153,9 @@
       <c r="K47" s="4"/>
       <c r="L47" s="6"/>
     </row>
-    <row r="48" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="7"/>
-      <c r="B48"/>
-      <c r="C48"/>
-      <c r="D48"/>
+    <row r="48" spans="1:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
       <c r="E48" s="5"/>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
@@ -1195,11 +1165,9 @@
       <c r="K48" s="4"/>
       <c r="L48" s="6"/>
     </row>
-    <row r="49" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="7"/>
-      <c r="B49"/>
-      <c r="C49"/>
-      <c r="D49"/>
+    <row r="49" spans="3:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
       <c r="E49" s="5"/>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
@@ -1209,7 +1177,7 @@
       <c r="K49" s="4"/>
       <c r="L49" s="6"/>
     </row>
-    <row r="50" spans="1:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="5"/>
@@ -1221,7 +1189,7 @@
       <c r="K50" s="4"/>
       <c r="L50" s="6"/>
     </row>
-    <row r="51" spans="1:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="5"/>
@@ -1233,11 +1201,11 @@
       <c r="K51" s="4"/>
       <c r="L51" s="6"/>
     </row>
-    <row r="52" spans="1:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:12" ht="12.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="5"/>
-      <c r="F52" s="4"/>
+      <c r="F52" s="5"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
@@ -1245,11 +1213,11 @@
       <c r="K52" s="4"/>
       <c r="L52" s="6"/>
     </row>
-    <row r="53" spans="1:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="5"/>
-      <c r="F53" s="4"/>
+      <c r="F53" s="5"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
@@ -1257,7 +1225,7 @@
       <c r="K53" s="4"/>
       <c r="L53" s="6"/>
     </row>
-    <row r="54" spans="1:12" ht="12.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
       <c r="E54" s="5"/>
@@ -1269,7 +1237,7 @@
       <c r="K54" s="4"/>
       <c r="L54" s="6"/>
     </row>
-    <row r="55" spans="1:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
       <c r="E55" s="5"/>
@@ -1281,7 +1249,7 @@
       <c r="K55" s="4"/>
       <c r="L55" s="6"/>
     </row>
-    <row r="56" spans="1:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
       <c r="E56" s="5"/>
@@ -1293,7 +1261,7 @@
       <c r="K56" s="4"/>
       <c r="L56" s="6"/>
     </row>
-    <row r="57" spans="1:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="5"/>
@@ -1305,7 +1273,7 @@
       <c r="K57" s="4"/>
       <c r="L57" s="6"/>
     </row>
-    <row r="58" spans="1:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
       <c r="E58" s="5"/>
@@ -1317,7 +1285,7 @@
       <c r="K58" s="4"/>
       <c r="L58" s="6"/>
     </row>
-    <row r="59" spans="1:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
       <c r="E59" s="5"/>
@@ -1329,7 +1297,7 @@
       <c r="K59" s="4"/>
       <c r="L59" s="6"/>
     </row>
-    <row r="60" spans="1:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="5"/>
@@ -1341,7 +1309,7 @@
       <c r="K60" s="4"/>
       <c r="L60" s="6"/>
     </row>
-    <row r="61" spans="1:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="5"/>
@@ -1353,7 +1321,7 @@
       <c r="K61" s="4"/>
       <c r="L61" s="6"/>
     </row>
-    <row r="62" spans="1:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C62" s="4"/>
       <c r="D62" s="4"/>
       <c r="E62" s="5"/>
@@ -1365,7 +1333,7 @@
       <c r="K62" s="4"/>
       <c r="L62" s="6"/>
     </row>
-    <row r="63" spans="1:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
       <c r="E63" s="5"/>
@@ -1377,7 +1345,7 @@
       <c r="K63" s="4"/>
       <c r="L63" s="6"/>
     </row>
-    <row r="64" spans="1:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C64" s="4"/>
       <c r="D64" s="4"/>
       <c r="E64" s="5"/>
@@ -2169,7 +2137,7 @@
       <c r="K129" s="4"/>
       <c r="L129" s="6"/>
     </row>
-    <row r="130" spans="3:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C130" s="4"/>
       <c r="D130" s="4"/>
       <c r="E130" s="5"/>
@@ -2181,28 +2149,14 @@
       <c r="K130" s="4"/>
       <c r="L130" s="6"/>
     </row>
-    <row r="131" spans="3:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C131" s="4"/>
-      <c r="D131" s="4"/>
-      <c r="E131" s="5"/>
-      <c r="F131" s="5"/>
-      <c r="G131" s="4"/>
-      <c r="H131" s="4"/>
-      <c r="I131" s="4"/>
-      <c r="J131" s="4"/>
-      <c r="K131" s="4"/>
+    <row r="131" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="E131" s="3"/>
+      <c r="F131" s="3"/>
       <c r="L131" s="6"/>
     </row>
     <row r="132" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C132" s="4"/>
-      <c r="D132" s="4"/>
-      <c r="E132" s="5"/>
-      <c r="F132" s="5"/>
-      <c r="G132" s="4"/>
-      <c r="H132" s="4"/>
-      <c r="I132" s="4"/>
-      <c r="J132" s="4"/>
-      <c r="K132" s="4"/>
+      <c r="E132" s="3"/>
+      <c r="F132" s="3"/>
       <c r="L132" s="6"/>
     </row>
     <row r="133" spans="3:12" x14ac:dyDescent="0.25">
@@ -3091,13 +3045,9 @@
       <c r="L309" s="6"/>
     </row>
     <row r="310" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E310" s="3"/>
-      <c r="F310" s="3"/>
       <c r="L310" s="6"/>
     </row>
     <row r="311" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E311" s="3"/>
-      <c r="F311" s="3"/>
       <c r="L311" s="6"/>
     </row>
     <row r="312" spans="5:12" x14ac:dyDescent="0.25">
@@ -3773,9 +3723,13 @@
       <c r="L535" s="6"/>
     </row>
     <row r="536" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E536" s="3"/>
+      <c r="F536" s="3"/>
       <c r="L536" s="6"/>
     </row>
     <row r="537" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E537" s="3"/>
+      <c r="F537" s="3"/>
       <c r="L537" s="6"/>
     </row>
     <row r="538" spans="5:12" x14ac:dyDescent="0.25">
@@ -4208,17 +4162,15 @@
       <c r="F623" s="3"/>
       <c r="L623" s="6"/>
     </row>
-    <row r="624" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E624" s="3"/>
-      <c r="F624" s="3"/>
+    <row r="624" spans="5:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L624" s="6"/>
     </row>
-    <row r="625" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E625" s="3"/>
-      <c r="F625" s="3"/>
+    <row r="625" spans="1:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A625" s="8"/>
       <c r="L625" s="6"/>
     </row>
     <row r="626" spans="1:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A626" s="8"/>
       <c r="L626" s="6"/>
     </row>
     <row r="627" spans="1:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -5569,16 +5521,18 @@
       <c r="A963" s="8"/>
       <c r="L963" s="6"/>
     </row>
-    <row r="964" spans="1:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="964" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A964" s="8"/>
       <c r="L964" s="6"/>
     </row>
-    <row r="965" spans="1:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A965" s="8"/>
+    <row r="965" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E965" s="3"/>
+      <c r="F965" s="3"/>
       <c r="L965" s="6"/>
     </row>
     <row r="966" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A966" s="8"/>
+      <c r="E966" s="3"/>
+      <c r="F966" s="3"/>
       <c r="L966" s="6"/>
     </row>
     <row r="967" spans="1:12" x14ac:dyDescent="0.25">
@@ -5961,19 +5915,17 @@
       <c r="F1042" s="3"/>
       <c r="L1042" s="6"/>
     </row>
-    <row r="1043" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E1043" s="3"/>
       <c r="F1043" s="3"/>
       <c r="L1043" s="6"/>
     </row>
-    <row r="1044" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E1044" s="3"/>
-      <c r="F1044" s="3"/>
+    <row r="1044" spans="1:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1044" s="8"/>
       <c r="L1044" s="6"/>
     </row>
     <row r="1045" spans="1:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E1045" s="3"/>
-      <c r="F1045" s="3"/>
+      <c r="A1045" s="8"/>
       <c r="L1045" s="6"/>
     </row>
     <row r="1046" spans="1:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -6320,20 +6272,12 @@
       <c r="A1131" s="8"/>
       <c r="L1131" s="6"/>
     </row>
-    <row r="1132" spans="1:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1132" s="8"/>
       <c r="L1132" s="6"/>
     </row>
-    <row r="1133" spans="1:12" ht="13" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1133" s="8"/>
+    <row r="1133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L1133" s="6"/>
-    </row>
-    <row r="1134" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1134" s="8"/>
-      <c r="L1134" s="6"/>
-    </row>
-    <row r="1135" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L1135" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
